--- a/research_CZ.xlsx
+++ b/research_CZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competitors" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not accessible" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Competitors" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Not accessible" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Competitors'!$A$1:$O$8</definedName>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R73"/>
+  <dimension ref="A1:R142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7002,6 +7002,5539 @@
       </c>
       <c r="R73" s="2">
         <f>IF(AND(Q73="yes",OR(N73="EXACT",N73="CLOSE"),ISNUMBER(M73)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>(6 ks) Polypropylenová nádoba GN 1/1 - Mléčná - Výška: 65 mm</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/6-ks-polypropylenova-nadoba-gn-1-1-mlecna-vyska-65-mm-gpp1165-6</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>1046.33</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M74" s="4">
+        <f>IF(OR(G74="",J74="",K74=""),"",ROUND(IF(I74="incl.",G74/(1+J74),G74)/IF(L74="per pack",K74,1),2))</f>
+        <v/>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Net CZK as displayed (gross 1,245.13 at German 19%); SKU GPP1165-6</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q74" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C74,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R74" s="2">
+        <f>IF(AND(Q74="yes",OR(N74="EXACT",N74="CLOSE"),ISNUMBER(M74)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba 1/1 100 polypropylen</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/gastronadoba-1-1-100-polypropylen--1814702-10/</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M75" s="4">
+        <f>IF(OR(G75="",J75="",K75=""),"",ROUND(IF(I75="incl.",G75/(1+J75),G75)/IF(L75="per pack",K75,1),2))</f>
+        <v/>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Code 1814702-10; PP GN 1/1 but 100 mm deep (PP 1/1 range is 100/150/200 mm only, no 65 mm); 266.20 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q75" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C75,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R75" s="2">
+        <f>IF(AND(Q75="yes",OR(N75="EXACT",N75="CLOSE"),ISNUMBER(M75)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Nádoba z polypropylenu, GN 1/1, 65 mm | STALGAST, Bufet</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/gastronadoby-polypropylenove/nadoba-z-polypropylenu-gn-1-1-65-mm-stalgast-bufet</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M76" s="4">
+        <f>IF(OR(G76="",J76="",K76=""),"",ROUND(IF(I76="incl.",G76/(1+J76),G76)/IF(L76="per pack",K76,1),2))</f>
+        <v/>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Lowest PP GN 1/1 65 listed; Cambro R-MP11065 234 CZK. (APS 82104 207 CZK named polycarbonate but listed under PP - conflicting, not used); price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q76" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C76,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R76" s="2">
+        <f>IF(AND(Q76="yes",OR(N76="EXACT",N76="CLOSE"),ISNUMBER(M76)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Pujadas gastro nádoba GN 1/1 530x325 mm polypropylen v=65 mm</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Pujadas</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/pujadas-gastro-nadoba-gn-1-1-530x325-mm-polypropylen-v-65-mm.html</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>443</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M77" s="4">
+        <f>IF(OR(G77="",J77="",K77=""),"",ROUND(IF(I77="incl.",G77/(1+J77),G77)/IF(L77="per pack",K77,1),2))</f>
+        <v/>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>366.12 CZK bez DPH; code 227705320; in stock (central warehouse)</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q77" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C77,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R77" s="2">
+        <f>IF(AND(Q77="yes",OR(N77="EXACT",N77="CLOSE"),ISNUMBER(M77)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba polypropylenová GN 1/1 65 mm</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/gastronadoba-polypropylenova-gn-1-1-65-mm/</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M78" s="4">
+        <f>IF(OR(G78="",J78="",K78=""),"",ROUND(IF(I78="incl.",G78/(1+J78),G78)/IF(L78="per pack",K78,1),2))</f>
+        <v/>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Code R-MP11065; 193 CZK bez DPH; in stock</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q78" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C78,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R78" s="2">
+        <f>IF(AND(Q78="yes",OR(N78="EXACT",N78="CLOSE"),ISNUMBER(M78)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>(12 ks) Gastronádoba GN 1/3 - polykarbonát - čirá - Výška: 100 mm</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/12-ks-gastronadoba-gn-1-3-polykarbonat-cira-vyska-100-mm-gpcp13100s</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>1606.13</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M79" s="4">
+        <f>IF(OR(G79="",J79="",K79=""),"",ROUND(IF(I79="incl.",G79/(1+J79),G79)/IF(L79="per pack",K79,1),2))</f>
+        <v/>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>SKU GPCP13100S; CZ title says 'čirá' (clear) while the same SKU is 'schwarz' on the German/Austrian storefronts</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q79" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C79,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R79" s="2">
+        <f>IF(AND(Q79="yes",OR(N79="EXACT",N79="CLOSE"),ISNUMBER(M79)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba PC 1/3 100</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/gastronadoba-pc-1-3-100--0835131/</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>159</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M80" s="4">
+        <f>IF(OR(G80="",J80="",K80=""),"",ROUND(IF(I80="incl.",G80/(1+J80),G80)/IF(L80="per pack",K80,1),2))</f>
+        <v/>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Code 0835131; 192.39 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q80" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C80,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R80" s="2">
+        <f>IF(AND(Q80="yes",OR(N80="EXACT",N80="CLOSE"),ISNUMBER(M80)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Gastro nádoba GN 1/3 100 mm, polykarbonát | YATO, YG-00411</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Yato</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/gastronadoby-polykarbonatove/gastro-nadoba-gn-1-3-100-mm-polykarbonat-yato-yg-00411</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M81" s="4">
+        <f>IF(OR(G81="",J81="",K81=""),"",ROUND(IF(I81="incl.",G81/(1+J81),G81)/IF(L81="per pack",K81,1),2))</f>
+        <v/>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Lowest PC GN 1/3 100; Stalgast Bufet PC 191, Cambro 229 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q81" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C81,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R81" s="2">
+        <f>IF(AND(Q81="yes",OR(N81="EXACT",N81="CLOSE"),ISNUMBER(M81)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>ARAVEN Gastronádoba GN 1/3, polykarbonát, hloubka: 100 mm, objem: 3,7 L</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Araven</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/araven-gn-nadoba-1-3-polykarbonat-hloubka-100-mm-objem-3-7-l.html</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M82" s="4">
+        <f>IF(OR(G82="",J82="",K82=""),"",ROUND(IF(I82="incl.",G82/(1+J82),G82)/IF(L82="per pack",K82,1),2))</f>
+        <v/>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>233.88 CZK bez DPH; lowest PC GN 1/3 100; alternatives APS 295, Pujadas 381 CZK</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q82" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C82,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R82" s="2">
+        <f>IF(AND(Q82="yes",OR(N82="EXACT",N82="CLOSE"),ISNUMBER(M82)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba polykarbonátová GN 1/3 100 mm</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/gastronadoba-polykarbonatova-gn-1-3-100-mm-2/</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>229</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M83" s="4">
+        <f>IF(OR(G83="",J83="",K83=""),"",ROUND(IF(I83="incl.",G83/(1+J83),G83)/IF(L83="per pack",K83,1),2))</f>
+        <v/>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Code R-M213100; 189 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q83" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C83,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R83" s="2">
+        <f>IF(AND(Q83="yes",OR(N83="EXACT",N83="CLOSE"),ISNUMBER(M83)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>(12 ks) Gastronádoba GN 1/2 - polypropylen - mléčná - Výška: 150 mm</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/12-ks-gastronadoba-gn-1-2-polypropylen-mlecna-vyska-150-mm-gpp12150</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>1216.71</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M84" s="4">
+        <f>IF(OR(G84="",J84="",K84=""),"",ROUND(IF(I84="incl.",G84/(1+J84),G84)/IF(L84="per pack",K84,1),2))</f>
+        <v/>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>SKU GPP12150</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q84" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C84,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R84" s="2">
+        <f>IF(AND(Q84="yes",OR(N84="EXACT",N84="CLOSE"),ISNUMBER(M84)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba 1/2 150 polypropylen</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/gastronadoba-1-2-150-polypropylen--1814705-15/</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M85" s="4">
+        <f>IF(OR(G85="",J85="",K85=""),"",ROUND(IF(I85="incl.",G85/(1+J85),G85)/IF(L85="per pack",K85,1),2))</f>
+        <v/>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Code 1814705-15; 169.40 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q85" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C85,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R85" s="2">
+        <f>IF(AND(Q85="yes",OR(N85="EXACT",N85="CLOSE"),ISNUMBER(M85)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Nádoba z polypropylenu, GN 1/2, 150 mm | STALGAST, Bufet</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/gastronadoby-polypropylenove/nadoba-z-polypropylenu-gn-1-2-150-mm-stalgast-bufet</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M86" s="4">
+        <f>IF(OR(G86="",J86="",K86=""),"",ROUND(IF(I86="incl.",G86/(1+J86),G86)/IF(L86="per pack",K86,1),2))</f>
+        <v/>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Cambro R-MP12150 227 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q86" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C86,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R86" s="2">
+        <f>IF(AND(Q86="yes",OR(N86="EXACT",N86="CLOSE"),ISNUMBER(M86)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>gastro nádoba GN 1/2 polypropylen v=150 mm Pujadas</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Pujadas</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/gastro-nadoba-gn-1-2-polypropylen-v-150-mm-pujadas.html</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>334</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M87" s="4">
+        <f>IF(OR(G87="",J87="",K87=""),"",ROUND(IF(I87="incl.",G87/(1+J87),G87)/IF(L87="per pack",K87,1),2))</f>
+        <v/>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>276.03 CZK bez DPH; in stock</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q87" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C87,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R87" s="2">
+        <f>IF(AND(Q87="yes",OR(N87="EXACT",N87="CLOSE"),ISNUMBER(M87)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba polypropylenová GN 1/2 150 mm</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/gastronadoba-polypropylenova-gn-1-2-150-mm-2/</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>227</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M88" s="4">
+        <f>IF(OR(G88="",J88="",K88=""),"",ROUND(IF(I88="incl.",G88/(1+J88),G88)/IF(L88="per pack",K88,1),2))</f>
+        <v/>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Code R-MP12150; 188 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q88" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C88,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R88" s="2">
+        <f>IF(AND(Q88="yes",OR(N88="EXACT",N88="CLOSE"),ISNUMBER(M88)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>(6 ks) GN kryt GN 1/1 - Polykarbonát - Výška: 35 mm</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/6-ks-gn-kryt-gn-1-1-polykarbonat-vyska-35-mm-82001-6</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>1679.15</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M89" s="4">
+        <f>IF(OR(G89="",J89="",K89=""),"",ROUND(IF(I89="incl.",G89/(1+J89),G89)/IF(L89="per pack",K89,1),2))</f>
+        <v/>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>PC lid 35 mm high (raised rather than flat standard lid)</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q89" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C89,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R89" s="2">
+        <f>IF(AND(Q89="yes",OR(N89="EXACT",N89="CLOSE"),ISNUMBER(M89)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Víko PC GN 1/1</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/viko-pc-gn-1-1--0835161/</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>249</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M90" s="4">
+        <f>IF(OR(G90="",J90="",K90=""),"",ROUND(IF(I90="incl.",G90/(1+J90),G90)/IF(L90="per pack",K90,1),2))</f>
+        <v/>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Code 0835161; polycarbonate plain lid; 301.29 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q90" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C90,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R90" s="2">
+        <f>IF(AND(Q90="yes",OR(N90="EXACT",N90="CLOSE"),ISNUMBER(M90)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Polykarbonátové víko, GN 1/1 | STALGAST, Bufet</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/vika-gn-polykarbonatove/polykarbonatove-viko-gn-1-1-stalgast-bufet</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M91" s="4">
+        <f>IF(OR(G91="",J91="",K91=""),"",ROUND(IF(I91="incl.",G91/(1+J91),G91)/IF(L91="per pack",K91,1),2))</f>
+        <v/>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Plain PC lid; Stalgast Premium clear lid 269 CZK (material not in name), Cambro R-M211001 357 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q91" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C91,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R91" s="2">
+        <f>IF(AND(Q91="yes",OR(N91="EXACT",N91="CLOSE"),ISNUMBER(M91)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>ARAVEN Víko na gastronádobu GN 1/1, polykarbonát, volné</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Araven</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/araven-gn-deckel-1-1-polykarbonat-volny.html</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M92" s="4">
+        <f>IF(OR(G92="",J92="",K92=""),"",ROUND(IF(I92="incl.",G92/(1+J92),G92)/IF(L92="per pack",K92,1),2))</f>
+        <v/>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>314.05 CZK bez DPH; plain loose PC lid; APS PC lid 394 CZK</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q92" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C92,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R92" s="2">
+        <f>IF(AND(Q92="yes",OR(N92="EXACT",N92="CLOSE"),ISNUMBER(M92)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Víko pro gastronádobu GN 1/1</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/viko-pro-gastronadobu-gn-1-1/</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>357</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M93" s="4">
+        <f>IF(OR(G93="",J93="",K93=""),"",ROUND(IF(I93="incl.",G93/(1+J93),G93)/IF(L93="per pack",K93,1),2))</f>
+        <v/>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Code R-M211001; material polykarbonát, plain lid, price per 1 piece; 295 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q93" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C93,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R93" s="2">
+        <f>IF(AND(Q93="yes",OR(N93="EXACT",N93="CLOSE"),ISNUMBER(M93)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>(12 ks) Polypropylenová nádoba GN 1/6 - Mléčná - Výška: 100 mm</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/12-ks-polypropylenova-nadoba-gn-1-6-mlecna-vyska-100-mm-gpp16100-12</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>1070.67</v>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M94" s="4">
+        <f>IF(OR(G94="",J94="",K94=""),"",ROUND(IF(I94="incl.",G94/(1+J94),G94)/IF(L94="per pack",K94,1),2))</f>
+        <v/>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q94" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C94,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R94" s="2">
+        <f>IF(AND(Q94="yes",OR(N94="EXACT",N94="CLOSE"),ISNUMBER(M94)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba 1/6 100 polypropylen</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/gastronadoba-1-6-100-polypropylen/</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M95" s="4">
+        <f>IF(OR(G95="",J95="",K95=""),"",ROUND(IF(I95="incl.",G95/(1+J95),G95)/IF(L95="per pack",K95,1),2))</f>
+        <v/>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Code 1814709-10; 90.75 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q95" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C95,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R95" s="2">
+        <f>IF(AND(Q95="yes",OR(N95="EXACT",N95="CLOSE"),ISNUMBER(M95)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Nádoba z polypropylenu, GN 1/6, 100 mm | STALGAST, Bufet</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/gastronadoby-polypropylenove/nadoba-z-polypropylenu-gn-1-6-100-mm-stalgast-bufet</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M96" s="4">
+        <f>IF(OR(G96="",J96="",K96=""),"",ROUND(IF(I96="incl.",G96/(1+J96),G96)/IF(L96="per pack",K96,1),2))</f>
+        <v/>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Cambro R-MP16100 94 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q96" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C96,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R96" s="2">
+        <f>IF(AND(Q96="yes",OR(N96="EXACT",N96="CLOSE"),ISNUMBER(M96)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Pujadas gastro nádoba GN 1/6 176x162 mm polypropylen v=100 mm</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Pujadas</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/pujadas-gastro-nadoba-gn-1-6-176x162-mm-polypropylen-v-100-mm.html</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M97" s="4">
+        <f>IF(OR(G97="",J97="",K97=""),"",ROUND(IF(I97="incl.",G97/(1+J97),G97)/IF(L97="per pack",K97,1),2))</f>
+        <v/>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>107.44 CZK bez DPH; APS PP alternative 137 CZK</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q97" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C97,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R97" s="2">
+        <f>IF(AND(Q97="yes",OR(N97="EXACT",N97="CLOSE"),ISNUMBER(M97)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba polypropylenová GN 1/6 100 mm</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/gastronadoba-polypropylenova-gn-1-6-100-mm-2/</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M98" s="4">
+        <f>IF(OR(G98="",J98="",K98=""),"",ROUND(IF(I98="incl.",G98/(1+J98),G98)/IF(L98="per pack",K98,1),2))</f>
+        <v/>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Code R-MP16100; 78 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q98" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C98,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R98" s="2">
+        <f>IF(AND(Q98="yes",OR(N98="EXACT",N98="CLOSE"),ISNUMBER(M98)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>(12 ks) Polypropylenová nádoba GN 1/9 - Mléčná - Výška: 100 mm</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/12-ks-polypropylenova-nadoba-gn-1-9-mlecna-vyska-100-mm-gpp19100-12</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>997.66</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M99" s="4">
+        <f>IF(OR(G99="",J99="",K99=""),"",ROUND(IF(I99="incl.",G99/(1+J99),G99)/IF(L99="per pack",K99,1),2))</f>
+        <v/>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr"/>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q99" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C99,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R99" s="2">
+        <f>IF(AND(Q99="yes",OR(N99="EXACT",N99="CLOSE"),ISNUMBER(M99)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Nádoba z polypropylénu GN 1/9, 100 mm | STALGAST, Bufet Safe</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/gastronadoby-polypropylenove/nadoba-z-polypropylenu-gn-1-9-100-mm-stalgast-bufet-safe</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M100" s="4">
+        <f>IF(OR(G100="",J100="",K100=""),"",ROUND(IF(I100="incl.",G100/(1+J100),G100)/IF(L100="per pack",K100,1),2))</f>
+        <v/>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>HENDI Profi Line PP 95, Cambro 105 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q100" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C100,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R100" s="2">
+        <f>IF(AND(Q100="yes",OR(N100="EXACT",N100="CLOSE"),ISNUMBER(M100)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>APS GN-nádoba Polypropylen, GN 1/9, objem: 1,00 litr, hloubka: 100 mm</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/aps-gn-nadoba-z-polypropylenu-gn-1-9-obsah-1-00-litru-hloubka-100-mm.html</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M101" s="4">
+        <f>IF(OR(G101="",J101="",K101=""),"",ROUND(IF(I101="incl.",G101/(1+J101),G101)/IF(L101="per pack",K101,1),2))</f>
+        <v/>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>102.48 CZK bez DPH; availability not shown as in stock; Pujadas PP 1/9 100 in stock 159 CZK</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q101" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C101,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R101" s="2">
+        <f>IF(AND(Q101="yes",OR(N101="EXACT",N101="CLOSE"),ISNUMBER(M101)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba polypropylenová GN 1/9 100 mm</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/gastronadoba-polypropylenova-gn-1-9-100-mm/</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M102" s="4">
+        <f>IF(OR(G102="",J102="",K102=""),"",ROUND(IF(I102="incl.",G102/(1+J102),G102)/IF(L102="per pack",K102,1),2))</f>
+        <v/>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Code R-MP19100; 87 CZK bez DPH. A clearance item MP-19100 (TOMGAST brand, "only until stock runs out") is 74 CZK incl.</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q102" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C102,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R102" s="2">
+        <f>IF(AND(Q102="yes",OR(N102="EXACT",N102="CLOSE"),ISNUMBER(M102)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Láhev plastová dávkovací čirá 354ml</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/lahev-plastova-davkovaci-cira-354ml--255046026/</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M103" s="4">
+        <f>IF(OR(G103="",J103="",K103=""),"",ROUND(IF(I103="incl.",G103/(1+J103),G103)/IF(L103="per pack",K103,1),2))</f>
+        <v/>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>354 ml instead of 250 ml; plastic type not stated. Smallest squeeze bottle listed; 35.09 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q103" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C103,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R103" s="2">
+        <f>IF(AND(Q103="yes",OR(N103="EXACT",N103="CLOSE"),ISNUMBER(M103)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Dávkovač na omáčky z polyethylenu 0,25 l průhledný | CONTACTO, 1460/251</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Contacto</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/davkovace-omacek/davkovac-na-omacky-z-polyethylenu-0-25-l-pruhledny-contacto-1460-251</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M104" s="4">
+        <f>IF(OR(G104="",J104="",K104=""),"",ROUND(IF(I104="incl.",G104/(1+J104),G104)/IF(L104="per pack",K104,1),2))</f>
+        <v/>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>250 ml but polyethylene (not PP); 35 CZK bez DPH shown; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q104" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C104,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R104" s="2">
+        <f>IF(AND(Q104="yes",OR(N104="EXACT",N104="CLOSE"),ISNUMBER(M104)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Araven Mini Dávkovací láhev na omáčky, obsah: 0,25 l</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Araven</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/araven-mini-davkovaci-lahvicka-obsah-0-25-l-vyska-167-mm-prumer-56-mm.html</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M105" s="4">
+        <f>IF(OR(G105="",J105="",K105=""),"",ROUND(IF(I105="incl.",G105/(1+J105),G105)/IF(L105="per pack",K105,1),2))</f>
+        <v/>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>81.82 CZK bez DPH; 250 ml but HDPE (not PP), screw cap. HENDI 0.2 l LDPE 67 CZK</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q105" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C105,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R105" s="2">
+        <f>IF(AND(Q105="yes",OR(N105="EXACT",N105="CLOSE"),ISNUMBER(M105)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Dávkovač na omáčky  250 ml</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Laco</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/davkovac-na-omacky--250-ml/</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M106" s="4">
+        <f>IF(OR(G106="",J106="",K106=""),"",ROUND(IF(I106="incl.",G106/(1+J106),G106)/IF(L106="per pack",K106,1),2))</f>
+        <v/>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Code E-61925; 250 ml but polyethylene (not PP); 43 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q106" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C106,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R106" s="2">
+        <f>IF(AND(Q106="yes",OR(N106="EXACT",N106="CLOSE"),ISNUMBER(M106)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>(6 ks) Stlačovací lahev na omáčky se středovou membránou - 710 ml</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/6-ks-stlacovaci-lahev-na-omacky-se-stredovou-membranou-710-ml-se-sroubovacim-uzaverem-a-uzaviraci-cepickou-ffo-004</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>827.28</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M107" s="4">
+        <f>IF(OR(G107="",J107="",K107=""),"",ROUND(IF(I107="incl.",G107/(1+J107),G107)/IF(L107="per pack",K107,1),2))</f>
+        <v/>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>710 ml FIFO bottle with valve, screw cap and closing cap; material not stated</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q107" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C107,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R107" s="2">
+        <f>IF(AND(Q107="yes",OR(N107="EXACT",N107="CLOSE"),ISNUMBER(M107)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Plastová láhev zdobící 708ml</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/plastova-lahev-zdobici-708ml--255047026/</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M108" s="4">
+        <f>IF(OR(G108="",J108="",K108=""),"",ROUND(IF(I108="incl.",G108/(1+J108),G108)/IF(L108="per pack",K108,1),2))</f>
+        <v/>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Code 255047026; 708 ml decorating squeeze bottle, single tip; plastic type not stated (flagged); 47.19 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q108" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C108,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R108" s="2">
+        <f>IF(AND(Q108="yes",OR(N108="EXACT",N108="CLOSE"),ISNUMBER(M108)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Dávkovač na omáčky 720 ml, transparentní | TOM-GAST, MA-966</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/davkovace-omacek/davkovac-na-omacky-720-ml-transparentni-tom-gast-ma-966</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M109" s="4">
+        <f>IF(OR(G109="",J109="",K109=""),"",ROUND(IF(I109="incl.",G109/(1+J109),G109)/IF(L109="per pack",K109,1),2))</f>
+        <v/>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>720 ml, polyethylene (not PP); Contacto PE 0.7 l 55 CZK, APS 0.76 l set of 6 361 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q109" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C109,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R109" s="2">
+        <f>IF(AND(Q109="yes",OR(N109="EXACT",N109="CLOSE"),ISNUMBER(M109)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>ARAVEN Mačkací láhev, LDPE, ø: 75 mm, výška: 273 mm, objem: 0,75 L, bílá</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Araven</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/araven-stlacovaci-lahev-ldpe-o-75-mm-vyska-273-mm-objem-0-75-l-bila.html</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>154</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M110" s="4">
+        <f>IF(OR(G110="",J110="",K110=""),"",ROUND(IF(I110="incl.",G110/(1+J110),G110)/IF(L110="per pack",K110,1),2))</f>
+        <v/>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>127.27 CZK bez DPH; 750 ml but LDPE (not PP). Cheaper: Contacto 700 ml PE 54 CZK, HENDI 0.7 l LDPE 74 CZK</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q110" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C110,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R110" s="2">
+        <f>IF(AND(Q110="yes",OR(N110="EXACT",N110="CLOSE"),ISNUMBER(M110)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Dávkovač na omáčky 720 ml, transparentní</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/davkovac-na-omacky-720-ml--transparentni/</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M111" s="4">
+        <f>IF(OR(G111="",J111="",K111=""),"",ROUND(IF(I111="incl.",G111/(1+J111),G111)/IF(L111="per pack",K111,1),2))</f>
+        <v/>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Code MA-966; 720 ml, polyethylene (not PP); 28 CZK bez DPH. Laco 700 ml (E-61970) is 64 CZK incl.</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q111" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C111,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R111" s="2">
+        <f>IF(AND(Q111="yes",OR(N111="EXACT",N111="CLOSE"),ISNUMBER(M111)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Krájecí deska - EN 250x400 - Dle HACCP - Červená</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/krajeci-deska-en-250x400-dle-haccp-cervena-sbp25r</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>413.52</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M112" s="4">
+        <f>IF(OR(G112="",J112="",K112=""),"",ROUND(IF(I112="incl.",G112/(1+J112),G112)/IF(L112="per pack",K112,1),2))</f>
+        <v/>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Red HACCP board but 250x400 mm (vs 400x300)</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q112" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C112,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R112" s="2">
+        <f>IF(AND(Q112="yes",OR(N112="EXACT",N112="CLOSE"),ISNUMBER(M112)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Krájecí deska HACCP, červená, 450x300 mm | HENDI, 827017</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Hendi</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/plastove-krajeci-desky-haccp/krajeci-deska-haccp-cervena-450x300-mm-hendi-827017</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M113" s="4">
+        <f>IF(OR(G113="",J113="",K113=""),"",ROUND(IF(I113="incl.",G113/(1+J113),G113)/IF(L113="per pack",K113,1),2))</f>
+        <v/>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Red PE but 450 x 300 mm (no 400 x 300 board listed); thickness not in title; 251 CZK bez DPH; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q113" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C113,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R113" s="2">
+        <f>IF(AND(Q113="yes",OR(N113="EXACT",N113="CLOSE"),ISNUMBER(M113)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Prkénko krájecí plastové 40x30x2 cm, s drážkou, bílé</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Gastro</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/gastro-prkenko-krajeci-plastove-40x30x2-cm-s-drazkou-bile.html</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>1082</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M114" s="4">
+        <f>IF(OR(G114="",J114="",K114=""),"",ROUND(IF(I114="incl.",G114/(1+J114),G114)/IF(L114="per pack",K114,1),2))</f>
+        <v/>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>894.21 CZK bez DPH; 400 x 300 x 20 mm with groove, but white (red only in 10 mm: 619 CZK incl.); material stated only as "Plast" (PE not confirmed)</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q114" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C114,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R114" s="2">
+        <f>IF(AND(Q114="yes",OR(N114="EXACT",N114="CLOSE"),ISNUMBER(M114)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Deska 450 × 300 × 13 mm, červená</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/deska-450--300--13-mm--cervena/</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>353</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M115" s="4">
+        <f>IF(OR(G115="",J115="",K115=""),"",ROUND(IF(I115="incl.",G115/(1+J115),G115)/IF(L115="per pack",K115,1),2))</f>
+        <v/>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Code T-3045-R; red PE but 450 x 300 x 13 mm (no red 400 x 300 x 20 listed); 292 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q115" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C115,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R115" s="2">
+        <f>IF(AND(Q115="yes",OR(N115="EXACT",N115="CLOSE"),ISNUMBER(M115)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>(9 tlg) Přepravka na těsto-set - 8 nádob &amp; 1 víko - EN 600x400 - Výška: 75 mm - Polypropylen</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/9-tlg-prepravka-na-testo-set-8-nadob-und-1-viko-en-600x400-vyska-75-mm-polypropylen-bila-tbpp647</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>1752.16</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M116" s="4">
+        <f>IF(OR(G116="",J116="",K116=""),"",ROUND(IF(I116="incl.",G116/(1+J116),G116)/IF(L116="per pack",K116,1),2))</f>
+        <v/>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Sold only as set of 8 PP boxes plus 1 lid; per-box price includes a share of the lid</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q116" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C116,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R116" s="2">
+        <f>IF(AND(Q116="yes",OR(N116="EXACT",N116="CLOSE"),ISNUMBER(M116)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Přepravka na pizzu 60x40x9cm</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/prepravka-na-pizzu-60x40x9cm--1841762-09/</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M117" s="4">
+        <f>IF(OR(G117="",J117="",K117=""),"",ROUND(IF(I117="incl.",G117/(1+J117),G117)/IF(L117="per pack",K117,1),2))</f>
+        <v/>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>600 x 400 x 90 mm (not 75 mm); material not stated on page. Availability "Na dotaz"; 471.90 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q117" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C117,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R117" s="2">
+        <f>IF(AND(Q117="yes",OR(N117="EXACT",N117="CLOSE"),ISNUMBER(M117)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Přepravka na pizzu 60x40x7,5 cm | TOM-GAST, ZT-6040</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/kose-na-pizza-testo/prepravka-na-pizzu-60x40x7-5-cm-tom-gast-zt-6040</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M118" s="4">
+        <f>IF(OR(G118="",J118="",K118=""),"",ROUND(IF(I118="incl.",G118/(1+J118),G118)/IF(L118="per pack",K118,1),2))</f>
+        <v/>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>PP 600 x 400 x 75 mm (same item as tomgast.cz); Hendi 880906 PET 75 mm 392, Contacto 2510/600 473 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q118" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C118,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R118" s="2">
+        <f>IF(AND(Q118="yes",OR(N118="EXACT",N118="CLOSE"),ISNUMBER(M118)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Nádoba AmerBox Kitchen Line na pizza těsto, 600 × 400 mm, 14 l</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>AmerBox (Hendi)</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/nadoba-na-pizza-testo-600x400-amerbox-kitchen-line-14l-600x400x-h-75mm.html</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M119" s="4">
+        <f>IF(OR(G119="",J119="",K119=""),"",ROUND(IF(I119="incl.",G119/(1+J119),G119)/IF(L119="per pack",K119,1),2))</f>
+        <v/>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>235.54 CZK bez DPH; code HEN-880906; 600 x 400 x 75 mm but PET (not PP); lid sold separately</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q119" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C119,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R119" s="2">
+        <f>IF(AND(Q119="yes",OR(N119="EXACT",N119="CLOSE"),ISNUMBER(M119)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Přepravka na pizzu 60 × 40 × 7,5 cm</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/prepravka-na-pizzu-60--40--7-5-cm/</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M120" s="4">
+        <f>IF(OR(G120="",J120="",K120=""),"",ROUND(IF(I120="incl.",G120/(1+J120),G120)/IF(L120="per pack",K120,1),2))</f>
+        <v/>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Code ZT-6040; PP, 600 x 400 x 75 mm, lid sold separately; 280 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q120" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C120,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R120" s="2">
+        <f>IF(AND(Q120="yes",OR(N120="EXACT",N120="CLOSE"),ISNUMBER(M120)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>(6 ks) Gastronádoba GN GN 1/1 - polykarbonát - černá - výška: 100 mm</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/6-ks-gastronadoba-gn-gn-1-1-polykarbonat-cerna-vyska-100-mm-gpcp11100s</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>1314.06</v>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M121" s="4">
+        <f>IF(OR(G121="",J121="",K121=""),"",ROUND(IF(I121="incl.",G121/(1+J121),G121)/IF(L121="per pack",K121,1),2))</f>
+        <v/>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Black PC</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q121" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C121,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R121" s="2">
+        <f>IF(AND(Q121="yes",OR(N121="EXACT",N121="CLOSE"),ISNUMBER(M121)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba PC 1/1 100</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/gastronadoba-pc-1-1-100--0835126/</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M122" s="4">
+        <f>IF(OR(G122="",J122="",K122=""),"",ROUND(IF(I122="incl.",G122/(1+J122),G122)/IF(L122="per pack",K122,1),2))</f>
+        <v/>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Code 0835126; availability "Na dotaz"; 349.69 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q122" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C122,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R122" s="2">
+        <f>IF(AND(Q122="yes",OR(N122="EXACT",N122="CLOSE"),ISNUMBER(M122)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Gastro nádoba GN 1/1 100 mm, polykarbonát | YATO, YG-00391</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Yato</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/gastronadoby-polykarbonatove/gastro-nadoba-gn-1-1-100-mm-polykarbonat-yato-yg-00391</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M123" s="4">
+        <f>IF(OR(G123="",J123="",K123=""),"",ROUND(IF(I123="incl.",G123/(1+J123),G123)/IF(L123="per pack",K123,1),2))</f>
+        <v/>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast Bufet PC 482, Cambro 509 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q123" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C123,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R123" s="2">
+        <f>IF(AND(Q123="yes",OR(N123="EXACT",N123="CLOSE"),ISNUMBER(M123)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>ARAVEN Gastronádoba GN 1/1, polykarbonát, hloubka: 100 mm, objem: 13,4 L</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Araven</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/araven-gn-nadoba-1-1-polykarbonat-hloubka-100-mm-objem-13-4-l.html</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>635</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M124" s="4">
+        <f>IF(OR(G124="",J124="",K124=""),"",ROUND(IF(I124="incl.",G124/(1+J124),G124)/IF(L124="per pack",K124,1),2))</f>
+        <v/>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>524.79 CZK bez DPH; APS 683, Pujadas 815 CZK</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q124" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C124,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R124" s="2">
+        <f>IF(AND(Q124="yes",OR(N124="EXACT",N124="CLOSE"),ISNUMBER(M124)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba polykarbonátová GN 1/1 100 mm</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/gastronadoba-polykarbonatova-gn-1-1-100-mm-2/</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>509</v>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M125" s="4">
+        <f>IF(OR(G125="",J125="",K125=""),"",ROUND(IF(I125="incl.",G125/(1+J125),G125)/IF(L125="per pack",K125,1),2))</f>
+        <v/>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Code R-M211100; 421 CZK bez DPH. Second PC line M2-11100 is 426 CZK incl.</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q125" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C125,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R125" s="2">
+        <f>IF(AND(Q125="yes",OR(N125="EXACT",N125="CLOSE"),ISNUMBER(M125)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>(12 ks) Gastronádoba polykarbonát GN 1/6 - Transparentní - Výška: 100 mm</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/12-ks-gastronadoba-polykarbonat-gn-1-6-transparentni-vyska-100-mm-gpcp16100</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>1143.69</v>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M126" s="4">
+        <f>IF(OR(G126="",J126="",K126=""),"",ROUND(IF(I126="incl.",G126/(1+J126),G126)/IF(L126="per pack",K126,1),2))</f>
+        <v/>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr"/>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q126" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C126,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R126" s="2">
+        <f>IF(AND(Q126="yes",OR(N126="EXACT",N126="CLOSE"),ISNUMBER(M126)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Gastro nádoba GN 1/6 100 mm, polykarbonát | YATO, YG-00426</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Yato</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/gastronadoby-polykarbonatove/gastro-nadoba-gn-1-6-100-mm-polykarbonat-yato-yg-00426</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M127" s="4">
+        <f>IF(OR(G127="",J127="",K127=""),"",ROUND(IF(I127="incl.",G127/(1+J127),G127)/IF(L127="per pack",K127,1),2))</f>
+        <v/>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>HENDI Profi Line PC 85, Cambro 138 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q127" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C127,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R127" s="2">
+        <f>IF(AND(Q127="yes",OR(N127="EXACT",N127="CLOSE"),ISNUMBER(M127)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>ARAVEN Gastronádoba GN 1/6, polykarbonát, hloubka: 100 mm, objem: 1,6 L</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Araven</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/araven-gn-nadoba-1-6-polykarbonat-hloubka-100-mm-objem-1-6-l.html</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M128" s="4">
+        <f>IF(OR(G128="",J128="",K128=""),"",ROUND(IF(I128="incl.",G128/(1+J128),G128)/IF(L128="per pack",K128,1),2))</f>
+        <v/>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>133.88 CZK bez DPH; APS 177-178, Pujadas 215 CZK</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q128" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C128,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R128" s="2">
+        <f>IF(AND(Q128="yes",OR(N128="EXACT",N128="CLOSE"),ISNUMBER(M128)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Gastronádoba polykarbonátová GN 1/6 100 mm</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/gastronadoba-polykarbonatova-gn-1-6-100-mm-2/</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M129" s="4">
+        <f>IF(OR(G129="",J129="",K129=""),"",ROUND(IF(I129="incl.",G129/(1+J129),G129)/IF(L129="per pack",K129,1),2))</f>
+        <v/>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Code R-M216100; 114 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q129" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C129,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R129" s="2">
+        <f>IF(AND(Q129="yes",OR(N129="EXACT",N129="CLOSE"),ISNUMBER(M129)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Krájecí deska - 325x530 mm - Dle HACCP - Červená</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>GGM</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/krajeci-deska-325x530-mm-dle-haccp-cervena-sbp53r</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>632.5700000000001</v>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J130" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M130" s="4">
+        <f>IF(OR(G130="",J130="",K130=""),"",ROUND(IF(I130="incl.",G130/(1+J130),G130)/IF(L130="per pack",K130,1),2))</f>
+        <v/>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Red PE; thickness not shown (white board of same series on the German site: 325x530x20 mm)</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q130" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C130,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R130" s="2">
+        <f>IF(AND(Q130="yes",OR(N130="EXACT",N130="CLOSE"),ISNUMBER(M130)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Deska polyethylen GN 1/1 53x32,5x2cm nožičky, PE-HD červená</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/deska-polyethylen-gn-1-1--53x32-5x2cm--nozicky-pe-hd--cervena/</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>1090</v>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M131" s="4">
+        <f>IF(OR(G131="",J131="",K131=""),"",ROUND(IF(I131="incl.",G131/(1+J131),G131)/IF(L131="per pack",K131,1),2))</f>
+        <v/>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Code 1842538-03; red HDPE 530 x 325 mm but 20 mm thick (not 15), with feet; 1318.90 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q131" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C131,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R131" s="2">
+        <f>IF(AND(Q131="yes",OR(N131="EXACT",N131="CLOSE"),ISNUMBER(M131)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Deska ke krájení s výřezem z červeného polypropylenu 53x32,5x1,5 cm | STALGAST, 341531</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/plastove-krajeci-desky-haccp/deska-ke-krajeni-s-vyrezem-z-cerveneho-polypropylenu-53x32-5x1-5-cm-stalgast-341531</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>653</v>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M132" s="4">
+        <f>IF(OR(G132="",J132="",K132=""),"",ROUND(IF(I132="incl.",G132/(1+J132),G132)/IF(L132="per pack",K132,1),2))</f>
+        <v/>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Red 530 x 325 x 15 mm but polypropylene (not PE), with cut-out; 540 CZK bez DPH. HENDI red PE GN 1/1 530x325x10 mm 359 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q132" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C132,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R132" s="2">
+        <f>IF(AND(Q132="yes",OR(N132="EXACT",N132="CLOSE"),ISNUMBER(M132)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Prkénko krájecí plastové 53x32,5x2 cm GN 1/1, s drážkou, červené</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Gastro</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/gastro-prkenko-krajeci-plastove-53x32-5x2-cm-gn-1-1-s-drazkou-cervene.html</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>1531</v>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M133" s="4">
+        <f>IF(OR(G133="",J133="",K133=""),"",ROUND(IF(I133="incl.",G133/(1+J133),G133)/IF(L133="per pack",K133,1),2))</f>
+        <v/>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>1265.29 CZK bez DPH; red 530 x 325 mm but 20 mm thick (not 15) and with groove; material stated only as "Plast" (PE not confirmed)</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q133" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C133,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R133" s="2">
+        <f>IF(AND(Q133="yes",OR(N133="EXACT",N133="CLOSE"),ISNUMBER(M133)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Deska 500 × 325 × 20 mm, červená</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/deska-500--325--20-mm--cervena/</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="n">
+        <v>1016</v>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M134" s="4">
+        <f>IF(OR(G134="",J134="",K134=""),"",ROUND(IF(I134="incl.",G134/(1+J134),G134)/IF(L134="per pack",K134,1),2))</f>
+        <v/>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Code 37-C; red PE but 500 x 325 x 20 mm, not 530 x 325 x 15; 840 CZK bez DPH. Red 500 x 300 x 15 with groove (38-C) is 835 CZK incl.</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q134" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C134,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R134" s="2">
+        <f>IF(AND(Q134="yes",OR(N134="EXACT",N134="CLOSE"),ISNUMBER(M134)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>GGM Gastro (CZ storefront)</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>(6 kusů) CAMBRO CAMWEAR polypropylenový GN kryt 1/3 - vzduchotěsný - mléčný</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ggmgastro.com/cs-cz-czk/6-kusu-cambro-camwear-r-polypropylenovy-gn-kryt-1-3-vzduchotesny-mlecny-30ppcwsc190</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>437.86</v>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="M135" s="4">
+        <f>IF(OR(G135="",J135="",K135=""),"",ROUND(IF(I135="incl.",G135/(1+J135),G135)/IF(L135="per pack",K135,1),2))</f>
+        <v/>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>Airtight PP lid</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q135" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C135,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R135" s="2">
+        <f>IF(AND(Q135="yes",OR(N135="EXACT",N135="CLOSE"),ISNUMBER(M135)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Gastro Novotný</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Víko GN polypropylen 1/3 čiré</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n"/>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>https://eshop.gastronovotny.cz/viko-gn-polypropylen-1-3-cire/</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>excl.</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M136" s="4">
+        <f>IF(OR(G136="",J136="",K136=""),"",ROUND(IF(I136="incl.",G136/(1+J136),G136)/IF(L136="per pack",K136,1),2))</f>
+        <v/>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Code 1814727-99; PP lid, also in red/blue/green/yellow at the same price; 72.60 CZK incl. VAT</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q136" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C136,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R136" s="2">
+        <f>IF(AND(Q136="yes",OR(N136="EXACT",N136="CLOSE"),ISNUMBER(M136)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Víko z polypropylenu pro nádoby, GN 1/3 | STALGAST, Bufet</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/vika-gn-polypropylenove/viko-z-polypropylenu-pro-nadoby-gn-1-3-stalgast-bufet</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M137" s="4">
+        <f>IF(OR(G137="",J137="",K137=""),"",ROUND(IF(I137="incl.",G137/(1+J137),G137)/IF(L137="per pack",K137,1),2))</f>
+        <v/>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>APS 61, Redfox 71 CZK; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q137" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C137,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R137" s="2">
+        <f>IF(AND(Q137="yes",OR(N137="EXACT",N137="CLOSE"),ISNUMBER(M137)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>víko na gastro nádobu GN 1/3 polypropylen Pujadas</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Pujadas</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/viko-na-gastro-nadobu-gn-1-3-polypropylen-pujadas.html</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M138" s="4">
+        <f>IF(OR(G138="",J138="",K138=""),"",ROUND(IF(I138="incl.",G138/(1+J138),G138)/IF(L138="per pack",K138,1),2))</f>
+        <v/>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>EXACT</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>149.59 CZK bez DPH; plain PP lid; Araven hermetic PP lid 216 CZK</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q138" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C138,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R138" s="2">
+        <f>IF(AND(Q138="yes",OR(N138="EXACT",N138="CLOSE"),ISNUMBER(M138)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Víko těsnicí ke gastronádobě 1/3 325 × 176 mm</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Cambro</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/viko-tesnici-ke-gastronadobe-1-3-325--176-mm/</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M139" s="4">
+        <f>IF(OR(G139="",J139="",K139=""),"",ROUND(IF(I139="incl.",G139/(1+J139),G139)/IF(L139="per pack",K139,1),2))</f>
+        <v/>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Code R-MP13001; material polypropylen, but a seal cover rather than a standard flat lid; 80 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q139" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C139,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R139" s="2">
+        <f>IF(AND(Q139="yes",OR(N139="EXACT",N139="CLOSE"),ISNUMBER(M139)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP/PE, wide covered tip</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Gastrozone</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>APS Láhev mačkací, Obsah: 0,70 litru, s uzavírací krytkou</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>APS</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastrozone.cz/aps-kompresni-lahev-obsah-0-70-litru-vyska-240-mm-prumer-70-mm.html</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M140" s="4">
+        <f>IF(OR(G140="",J140="",K140=""),"",ROUND(IF(I140="incl.",G140/(1+J140),G140)/IF(L140="per pack",K140,1),2))</f>
+        <v/>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>80.99 CZK bez DPH; 700 ml PE squeeze bottle with closing cap over the tip (interpreted as covered tip); not 750 ml</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q140" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C140,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R140" s="2">
+        <f>IF(AND(Q140="yes",OR(N140="EXACT",N140="CLOSE"),ISNUMBER(M140)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 300x200x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Deska krájecí 20 × 30 × 1,2 cm</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>TOMGAST</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tomgast.cz/deska-krajeci-20--30--1-2-cm/</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M141" s="4">
+        <f>IF(OR(G141="",J141="",K141=""),"",ROUND(IF(I141="incl.",G141/(1+J141),G141)/IF(L141="per pack",K141,1),2))</f>
+        <v/>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>APPROX</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>PE 300 x 200 mm but 12 mm thick and white only (no red 300 x 200 x 20 listed); 95 CZK bez DPH</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q141" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C141,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R141" s="2">
+        <f>IF(AND(Q141="yes",OR(N141="EXACT",N141="CLOSE"),ISNUMBER(M141)),"yes","no")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 400x300x100 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Gastromania</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Nádoba na pizza těsto 400x300x100 mm | STALGAST, 563411</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Stalgast</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gastromania.cz/kose-na-pizza-testo/nadoba-na-pizza-testo-400x300x100-mm-stalgast-563411</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>336</v>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>CZK</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>incl.</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>per piece</t>
+        </is>
+      </c>
+      <c r="M142" s="4">
+        <f>IF(OR(G142="",J142="",K142=""),"",ROUND(IF(I142="incl.",G142/(1+J142),G142)/IF(L142="per pack",K142,1),2))</f>
+        <v/>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>400 x 300 x 100 mm but polyethylene (not PP); 278 CZK bez DPH; price incl. 21% VAT as published in product data (current price, in stock)</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Q142" s="2">
+        <f>IFERROR(INDEX(Competitors!$N$2:$N$50,MATCH(C142,Competitors!$A$2:$A$50,0)),"no")</f>
+        <v/>
+      </c>
+      <c r="R142" s="2">
+        <f>IF(AND(Q142="yes",OR(N142="EXACT",N142="CLOSE"),ISNUMBER(M142)),"yes","no")</f>
         <v/>
       </c>
     </row>
@@ -7091,7 +12624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7798,52 +13331,706 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PP, 65 mm</t>
+        </is>
+      </c>
+      <c r="C19" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A19,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D19" s="4">
+        <f t="array" ref="D19">IF(C19=0,"",MIN(IF((Prices!$A$2:$A$600=A19)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E19" s="4">
+        <f t="array" ref="E19">IF(C19=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A19)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F19" s="4">
+        <f t="array" ref="F19">IF(C19=0,"",MAX(IF((Prices!$A$2:$A$600=A19)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G19" s="2">
+        <f t="array" ref="G19">IF(C19=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A19)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H19" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A19,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I19" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A19)</f>
+        <v/>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C20" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A20,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D20" s="4">
+        <f t="array" ref="D20">IF(C20=0,"",MIN(IF((Prices!$A$2:$A$600=A20)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f t="array" ref="E20">IF(C20=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A20)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f t="array" ref="F20">IF(C20=0,"",MAX(IF((Prices!$A$2:$A$600=A20)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G20" s="2">
+        <f t="array" ref="G20">IF(C20=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A20)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H20" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A20,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I20" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/2 container, PP, 150 mm</t>
+        </is>
+      </c>
+      <c r="C21" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A21,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D21" s="4">
+        <f t="array" ref="D21">IF(C21=0,"",MIN(IF((Prices!$A$2:$A$600=A21)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E21" s="4">
+        <f t="array" ref="E21">IF(C21=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A21)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F21" s="4">
+        <f t="array" ref="F21">IF(C21=0,"",MAX(IF((Prices!$A$2:$A$600=A21)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="2">
+        <f t="array" ref="G21">IF(C21=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A21)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H21" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A21,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I21" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 PC lid, standard</t>
+        </is>
+      </c>
+      <c r="C22" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A22,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D22" s="4">
+        <f t="array" ref="D22">IF(C22=0,"",MIN(IF((Prices!$A$2:$A$600=A22)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E22" s="4">
+        <f t="array" ref="E22">IF(C22=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A22)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="4">
+        <f t="array" ref="F22">IF(C22=0,"",MAX(IF((Prices!$A$2:$A$600=A22)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="2">
+        <f t="array" ref="G22">IF(C22=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A22)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H22" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A22,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I22" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C23" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A23,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f t="array" ref="D23">IF(C23=0,"",MIN(IF((Prices!$A$2:$A$600=A23)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E23" s="4">
+        <f t="array" ref="E23">IF(C23=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A23)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f t="array" ref="F23">IF(C23=0,"",MAX(IF((Prices!$A$2:$A$600=A23)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="2">
+        <f t="array" ref="G23">IF(C23=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A23)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H23" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A23,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I23" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/9 container, PP, 100 mm</t>
+        </is>
+      </c>
+      <c r="C24" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A24,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D24" s="4">
+        <f t="array" ref="D24">IF(C24=0,"",MIN(IF((Prices!$A$2:$A$600=A24)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E24" s="4">
+        <f t="array" ref="E24">IF(C24=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A24)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F24" s="4">
+        <f t="array" ref="F24">IF(C24=0,"",MAX(IF((Prices!$A$2:$A$600=A24)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="2">
+        <f t="array" ref="G24">IF(C24=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A24)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H24" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A24,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I24" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 250 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C25" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A25,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D25" s="4">
+        <f t="array" ref="D25">IF(C25=0,"",MIN(IF((Prices!$A$2:$A$600=A25)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E25" s="4">
+        <f t="array" ref="E25">IF(C25=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A25)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F25" s="4">
+        <f t="array" ref="F25">IF(C25=0,"",MAX(IF((Prices!$A$2:$A$600=A25)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="2">
+        <f t="array" ref="G25">IF(C25=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A25)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H25" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A25,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I25" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP, single tip</t>
+        </is>
+      </c>
+      <c r="C26" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A26,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f t="array" ref="D26">IF(C26=0,"",MIN(IF((Prices!$A$2:$A$600=A26)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E26" s="4">
+        <f t="array" ref="E26">IF(C26=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A26)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F26" s="4">
+        <f t="array" ref="F26">IF(C26=0,"",MAX(IF((Prices!$A$2:$A$600=A26)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="2">
+        <f t="array" ref="G26">IF(C26=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A26)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H26" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A26,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I26" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 400x300x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C27" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A27,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D27" s="4">
+        <f t="array" ref="D27">IF(C27=0,"",MIN(IF((Prices!$A$2:$A$600=A27)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E27" s="4">
+        <f t="array" ref="E27">IF(C27=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A27)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F27" s="4">
+        <f t="array" ref="F27">IF(C27=0,"",MAX(IF((Prices!$A$2:$A$600=A27)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="2">
+        <f t="array" ref="G27">IF(C27=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A27)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H27" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A27,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I27" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 600x400x75 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C28" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A28,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D28" s="4">
+        <f t="array" ref="D28">IF(C28=0,"",MIN(IF((Prices!$A$2:$A$600=A28)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E28" s="4">
+        <f t="array" ref="E28">IF(C28=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A28)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="4">
+        <f t="array" ref="F28">IF(C28=0,"",MAX(IF((Prices!$A$2:$A$600=A28)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="2">
+        <f t="array" ref="G28">IF(C28=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A28)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H28" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A28,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I28" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/1 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C29" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A29,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D29" s="4">
+        <f t="array" ref="D29">IF(C29=0,"",MIN(IF((Prices!$A$2:$A$600=A29)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E29" s="4">
+        <f t="array" ref="E29">IF(C29=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A29)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F29" s="4">
+        <f t="array" ref="F29">IF(C29=0,"",MAX(IF((Prices!$A$2:$A$600=A29)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G29" s="2">
+        <f t="array" ref="G29">IF(C29=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A29)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H29" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A29,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I29" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/6 container, PC, 100 mm</t>
+        </is>
+      </c>
+      <c r="C30" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A30,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D30" s="4">
+        <f t="array" ref="D30">IF(C30=0,"",MIN(IF((Prices!$A$2:$A$600=A30)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E30" s="4">
+        <f t="array" ref="E30">IF(C30=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A30)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F30" s="4">
+        <f t="array" ref="F30">IF(C30=0,"",MAX(IF((Prices!$A$2:$A$600=A30)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G30" s="2">
+        <f t="array" ref="G30">IF(C30=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A30)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H30" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A30,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I30" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 530x325x15 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C31" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A31,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D31" s="4">
+        <f t="array" ref="D31">IF(C31=0,"",MIN(IF((Prices!$A$2:$A$600=A31)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E31" s="4">
+        <f t="array" ref="E31">IF(C31=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A31)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F31" s="4">
+        <f t="array" ref="F31">IF(C31=0,"",MAX(IF((Prices!$A$2:$A$600=A31)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G31" s="2">
+        <f t="array" ref="G31">IF(C31=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A31)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H31" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A31,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I31" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>GN 1/3 PP lid, standard</t>
+        </is>
+      </c>
+      <c r="C32" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A32,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D32" s="4">
+        <f t="array" ref="D32">IF(C32=0,"",MIN(IF((Prices!$A$2:$A$600=A32)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E32" s="4">
+        <f t="array" ref="E32">IF(C32=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A32)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F32" s="4">
+        <f t="array" ref="F32">IF(C32=0,"",MAX(IF((Prices!$A$2:$A$600=A32)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G32" s="2">
+        <f t="array" ref="G32">IF(C32=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A32)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H32" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A32,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I32" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Squeeze bottle 750 ml, PP/PE, wide covered tip</t>
+        </is>
+      </c>
+      <c r="C33" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A33,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D33" s="4">
+        <f t="array" ref="D33">IF(C33=0,"",MIN(IF((Prices!$A$2:$A$600=A33)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E33" s="4">
+        <f t="array" ref="E33">IF(C33=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A33)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F33" s="4">
+        <f t="array" ref="F33">IF(C33=0,"",MAX(IF((Prices!$A$2:$A$600=A33)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G33" s="2">
+        <f t="array" ref="G33">IF(C33=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A33)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H33" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A33,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I33" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Cutting board 300x200x20 mm, red PE</t>
+        </is>
+      </c>
+      <c r="C34" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A34,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D34" s="4">
+        <f t="array" ref="D34">IF(C34=0,"",MIN(IF((Prices!$A$2:$A$600=A34)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E34" s="4">
+        <f t="array" ref="E34">IF(C34=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A34)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F34" s="4">
+        <f t="array" ref="F34">IF(C34=0,"",MAX(IF((Prices!$A$2:$A$600=A34)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G34" s="2">
+        <f t="array" ref="G34">IF(C34=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A34)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H34" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A34,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I34" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Dough box 400x300x100 mm, PP, without lid</t>
+        </is>
+      </c>
+      <c r="C35" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A35,Prices!$R$2:$R$600,"yes")</f>
+        <v/>
+      </c>
+      <c r="D35" s="4">
+        <f t="array" ref="D35">IF(C35=0,"",MIN(IF((Prices!$A$2:$A$600=A35)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f t="array" ref="E35">IF(C35=0,"",MEDIAN(IF((Prices!$A$2:$A$600=A35)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f t="array" ref="F35">IF(C35=0,"",MAX(IF((Prices!$A$2:$A$600=A35)*(Prices!$R$2:$R$600="yes"),Prices!$M$2:$M$600)))</f>
+        <v/>
+      </c>
+      <c r="G35" s="2">
+        <f t="array" ref="G35">IF(C35=0,"",_xlfn.TEXTJOIN(", ",TRUE,IF((Prices!$A$2:$A$600=A35)*(Prices!$R$2:$R$600="yes"),Prices!$C$2:$C$600,"")))</f>
+        <v/>
+      </c>
+      <c r="H35" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A35,Prices!$N$2:$N$600,"APPROX")</f>
+        <v/>
+      </c>
+      <c r="I35" s="2">
+        <f>COUNTIFS(Prices!$A$2:$A$600,A35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>Notes:</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Statistics use only primary observations with match quality EXACT or CLOSE from competitors marked Counted = yes on the Competitors sheet (max one observation per competitor per item).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Net price per piece = listed price / (1 + VAT rate) when the listed price includes VAT, divided by pack size when the price is per pack. Czech VAT 21%.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Blank statistics = no qualifying observation. APPROX matches are listed on the Prices sheet but excluded from statistics.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Where several products matched equally well, the lowest current 1-unit price was taken as primary; alternatives, promotions and pack sizes are in the Prices notes.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>GGM Gastro prices are shown net on its CZ storefront (gross uses German 19% VAT, recorded in the VAT-rate column); net per piece is taken directly from the displayed net price. All other shops use Czech 21% VAT.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Prices checked 2026-09-30. All prices in CZK from Czech storefronts. MAKRO (login-only prices) and A GASTRO (site blocked) are not counted - see Not accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Items 18-34 (additional variants) added 2026-09-30 for the same competitors; same rules (EXACT/CLOSE only in statistics, net = gross/1.21 for Czech VAT, GGM uses its own net CZK).</t>
         </is>
       </c>
     </row>
